--- a/tools/importer/reports/import-standalone.report.xlsx
+++ b/tools/importer/reports/import-standalone.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="814">
   <si>
     <t>_reportFile</t>
   </si>
@@ -151,6 +151,21 @@
     <t>https://www.moogparts.com/installation-guide-search.html</t>
   </si>
   <si>
+    <t>legal.report.json</t>
+  </si>
+  <si>
+    <t>legal</t>
+  </si>
+  <si>
+    <t>2026-06-28T17:50:52.573Z</t>
+  </si>
+  <si>
+    <t>Privacy Policy | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/legal.html</t>
+  </si>
+  <si>
     <t>light-commercial-vehicle.report.json</t>
   </si>
   <si>
@@ -169,6 +184,27 @@
     <t>https://www.moogparts.com/light-commercial-vehicle.html</t>
   </si>
   <si>
+    <t>moognews.report.json</t>
+  </si>
+  <si>
+    <t>["hero-overlay","cards-article"]</t>
+  </si>
+  <si>
+    <t>moognews</t>
+  </si>
+  <si>
+    <t>news-index</t>
+  </si>
+  <si>
+    <t>2026-06-28T17:52:25.392Z</t>
+  </si>
+  <si>
+    <t>Automotive News | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/moognews.html</t>
+  </si>
+  <si>
     <t>parts-matter.report.json</t>
   </si>
   <si>
@@ -259,7 +295,7 @@
     <t>where-to-buy</t>
   </si>
   <si>
-    <t>2026-06-28T17:50:08.128Z</t>
+    <t>2026-06-29T04:39:19.417Z</t>
   </si>
   <si>
     <t>Where to Buy: MOOG Distributors &amp; Dealers Locator</t>
@@ -268,6 +304,186 @@
     <t>https://www.moogparts.com/where-to-buy.html</t>
   </si>
   <si>
+    <t>legal/anti-human-trafficking.report.json</t>
+  </si>
+  <si>
+    <t>legal/anti-human-trafficking</t>
+  </si>
+  <si>
+    <t>2026-06-28T17:50:59.920Z</t>
+  </si>
+  <si>
+    <t>Anti-Human Trafficking | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/legal/anti-human-trafficking.html</t>
+  </si>
+  <si>
+    <t>legal/privacy-policy.report.json</t>
+  </si>
+  <si>
+    <t>legal/privacy-policy</t>
+  </si>
+  <si>
+    <t>2026-06-28T17:51:07.452Z</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/legal/privacy-policy.html</t>
+  </si>
+  <si>
+    <t>legal/social-rules.report.json</t>
+  </si>
+  <si>
+    <t>legal/social-rules</t>
+  </si>
+  <si>
+    <t>2026-06-28T17:51:13.916Z</t>
+  </si>
+  <si>
+    <t>Social Media Sweepstakes Official Rules | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/legal/social-rules.html</t>
+  </si>
+  <si>
+    <t>legal/terms-conditions.report.json</t>
+  </si>
+  <si>
+    <t>legal/terms-conditions</t>
+  </si>
+  <si>
+    <t>2026-06-28T17:51:21.525Z</t>
+  </si>
+  <si>
+    <t>Terms and Conditions | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/legal/terms-conditions.html</t>
+  </si>
+  <si>
+    <t>legal/warranty.report.json</t>
+  </si>
+  <si>
+    <t>legal/warranty</t>
+  </si>
+  <si>
+    <t>2026-06-28T17:51:27.938Z</t>
+  </si>
+  <si>
+    <t>Warranty | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/legal/warranty.html</t>
+  </si>
+  <si>
+    <t>moognews/expands-parts-offering-in-october-2019.report.json</t>
+  </si>
+  <si>
+    <t>moognews/expands-parts-offering-in-october-2019</t>
+  </si>
+  <si>
+    <t>content-article</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:34:41.226Z</t>
+  </si>
+  <si>
+    <t>MOOG Expands Parts Offering in October | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/moognews/expands-parts-offering-in-october-2019.html</t>
+  </si>
+  <si>
+    <t>moognews/moog-announces-new-control-arm-part-numbers.report.json</t>
+  </si>
+  <si>
+    <t>moognews/moog-announces-new-control-arm-part-numbers</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:34:48.760Z</t>
+  </si>
+  <si>
+    <t>New Ball Joint Technology | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/moognews/moog-announces-new-control-arm-part-numbers.html</t>
+  </si>
+  <si>
+    <t>moognews/moog-announces-part-numbers-expansion-in-january-february.report.json</t>
+  </si>
+  <si>
+    <t>moognews/moog-announces-part-numbers-expansion-in-january-february</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:34:55.647Z</t>
+  </si>
+  <si>
+    <t>MOOG® Announces Part Numbers Expansion in January and February</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/moognews/moog-announces-part-numbers-expansion-in-january-february.html</t>
+  </si>
+  <si>
+    <t>moognews/moog-continues-product-expansion-into-2019.report.json</t>
+  </si>
+  <si>
+    <t>moognews/moog-continues-product-expansion-into-2019</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:35:01.412Z</t>
+  </si>
+  <si>
+    <t>MOOG® Steering and Suspension Continues its Product Expansion in 2019</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/moognews/moog-continues-product-expansion-into-2019.html</t>
+  </si>
+  <si>
+    <t>moognews/moog-creates-enhancements-premium-control-arms-providing-greater-durability-reliability.report.json</t>
+  </si>
+  <si>
+    <t>moognews/moog-creates-enhancements-premium-control-arms-providing-greater-durability-reliability</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:35:09.226Z</t>
+  </si>
+  <si>
+    <t>Premium Control Arm Enhancements | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/moognews/moog-creates-enhancements-premium-control-arms-providing-greater-durability-reliability.html</t>
+  </si>
+  <si>
+    <t>moognews/moog-releases-over-70-new-part-numbers.report.json</t>
+  </si>
+  <si>
+    <t>moognews/moog-releases-over-70-new-part-numbers</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:34:33.952Z</t>
+  </si>
+  <si>
+    <t>MOOG® Releases Over 70 New Part Numbers</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/moognews/MOOG-Releases-Over-70-New-Part-Numbers.html</t>
+  </si>
+  <si>
+    <t>moognews/solid-sway-bar-kits-release.report.json</t>
+  </si>
+  <si>
+    <t>moognews/solid-sway-bar-kits-release</t>
+  </si>
+  <si>
+    <t>2026-06-28T17:52:33.695Z</t>
+  </si>
+  <si>
+    <t>New Solid Sway Bar Kits Released | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/moognews/solid-sway-bar-kits-release.html</t>
+  </si>
+  <si>
     <t>parts/driveline.report.json</t>
   </si>
   <si>
@@ -352,9 +568,6 @@
     <t>parts-matter/adjusting-your-car-alignment</t>
   </si>
   <si>
-    <t>content-article</t>
-  </si>
-  <si>
     <t>2026-06-28T17:31:07.540Z</t>
   </si>
   <si>
@@ -364,6 +577,69 @@
     <t>https://www.moogparts.com/parts-matter/adjusting-your-car-alignment.html</t>
   </si>
   <si>
+    <t>parts-matter/all-about-ball-joints.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/all-about-ball-joints</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:25:46.060Z</t>
+  </si>
+  <si>
+    <t>All About Ball Joints | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/all-about-ball-joints.html</t>
+  </si>
+  <si>
+    <t>parts-matter/all-about-hub-assemblies.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/all-about-hub-assemblies</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:25:54.514Z</t>
+  </si>
+  <si>
+    <t>All About Wheel Hub Assemblies | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/all-about-hub-assemblies.html</t>
+  </si>
+  <si>
+    <t>parts-matter/all-about-tie-rods.report.json</t>
+  </si>
+  <si>
+    <t>["hero-overlay","hero-overlay"]</t>
+  </si>
+  <si>
+    <t>parts-matter/all-about-tie-rods</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:26:02.068Z</t>
+  </si>
+  <si>
+    <t>What Do Tie Rods Do? | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/all-about-tie-rods.html</t>
+  </si>
+  <si>
+    <t>parts-matter/ball-joints-tie-rods-whats-the-difference.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/ball-joints-tie-rods-whats-the-difference</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:26:10.146Z</t>
+  </si>
+  <si>
+    <t>The Difference Between Ball Joints and Tie Rods | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/ball-joints-tie-rods-whats-the-difference.html</t>
+  </si>
+  <si>
     <t>parts-matter/car-alignment.report.json</t>
   </si>
   <si>
@@ -379,6 +655,96 @@
     <t>https://www.moogparts.com/parts-matter/car-alignment.html</t>
   </si>
   <si>
+    <t>parts-matter/dangers-of-potholes.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/dangers-of-potholes</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:26:16.438Z</t>
+  </si>
+  <si>
+    <t>What are the Dangers of Potholes? | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/dangers-of-potholes.html</t>
+  </si>
+  <si>
+    <t>parts-matter/difference-between-tire-alignment-rotation.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/difference-between-tire-alignment-rotation</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:26:23.824Z</t>
+  </si>
+  <si>
+    <t>Difference Between Alignments and Rotations | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/difference-between-tire-alignment-rotation.html</t>
+  </si>
+  <si>
+    <t>parts-matter/failing-driveshaft.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/failing-driveshaft</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:26:30.747Z</t>
+  </si>
+  <si>
+    <t>Is Your Driveshaft Failing? | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/failing-driveshaft.html</t>
+  </si>
+  <si>
+    <t>parts-matter/five-ways-bad-alignment-wrecks-tires.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/five-ways-bad-alignment-wrecks-tires</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:26:39.272Z</t>
+  </si>
+  <si>
+    <t>Tires Wrecked from Bad Alignment | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/five-ways-bad-alignment-wrecks-tires.html</t>
+  </si>
+  <si>
+    <t>parts-matter/guide-to-control-arms.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/guide-to-control-arms</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:26:46.857Z</t>
+  </si>
+  <si>
+    <t>Guide to Control Arms | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/guide-to-control-arms.html</t>
+  </si>
+  <si>
+    <t>parts-matter/how-often-should-my-suspension-steering-systems-be-inspected.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/how-often-should-my-suspension-steering-systems-be-inspected</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:26:52.880Z</t>
+  </si>
+  <si>
+    <t>When to Get Your Steering &amp; Suspension Checked | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/how-often-should-my-suspension-steering-systems-be-inspected.html</t>
+  </si>
+  <si>
     <t>parts-matter/how-to-tell-if-you-have-a-bad-universal-joint.report.json</t>
   </si>
   <si>
@@ -394,6 +760,36 @@
     <t>https://www.moogparts.com/parts-matter/How-to-Tell-If-You-Have-a-Bad-Universal-Joint.html</t>
   </si>
   <si>
+    <t>parts-matter/parts-of-a-car.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/parts-of-a-car</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:27:00.631Z</t>
+  </si>
+  <si>
+    <t>Parts of Car Diagram | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/parts-of-a-car.html</t>
+  </si>
+  <si>
+    <t>parts-matter/pothole-damage-to-cars.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/pothole-damage-to-cars</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:27:08.264Z</t>
+  </si>
+  <si>
+    <t>Pothole Damage to Car Suspension | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/pothole-damage-to-cars.html</t>
+  </si>
+  <si>
     <t>parts-matter/signs-of-a-failing-control-arm.report.json</t>
   </si>
   <si>
@@ -424,6 +820,48 @@
     <t>https://www.moogparts.com/parts-matter/signs-you-need-an-alignment.html</t>
   </si>
   <si>
+    <t>parts-matter/surviving-pothole-season-old.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/surviving-pothole-season-old</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:27:16.015Z</t>
+  </si>
+  <si>
+    <t>Avoiding Pothole Damage to Your Vehicle | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/surviving-pothole-season-old.html</t>
+  </si>
+  <si>
+    <t>parts-matter/surviving-pothole-season.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/surviving-pothole-season</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:27:23.636Z</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/surviving-pothole-season.html</t>
+  </si>
+  <si>
+    <t>parts-matter/symptoms-of-bad-ball-joints.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/symptoms-of-bad-ball-joints</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:27:31.568Z</t>
+  </si>
+  <si>
+    <t>Symptoms of Bad Ball Joints | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/symptoms-of-bad-ball-joints.html</t>
+  </si>
+  <si>
     <t>parts-matter/symptoms-of-bad-sway-bar-links.report.json</t>
   </si>
   <si>
@@ -439,6 +877,21 @@
     <t>https://www.moogparts.com/parts-matter/Symptoms-of-Bad-Sway-Bar-Links.html</t>
   </si>
   <si>
+    <t>parts-matter/symptoms-of-bad-tie-rods.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/symptoms-of-bad-tie-rods</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:27:39.797Z</t>
+  </si>
+  <si>
+    <t>Symptoms of Bad Tie Rods | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/symptoms-of-bad-tie-rods.html</t>
+  </si>
+  <si>
     <t>parts-matter/what-are-u-joints.report.json</t>
   </si>
   <si>
@@ -454,6 +907,21 @@
     <t>https://www.moogparts.com/parts-matter/What-Are-U-Joints.html</t>
   </si>
   <si>
+    <t>parts-matter/what-causes-grinding-noise-under-my-car.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/what-causes-grinding-noise-under-my-car</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:27:48.394Z</t>
+  </si>
+  <si>
+    <t>Grinding Noises When Driving | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/what-causes-grinding-noise-under-my-car.html</t>
+  </si>
+  <si>
     <t>parts-matter/what-is-a-cv-axle.report.json</t>
   </si>
   <si>
@@ -484,6 +952,51 @@
     <t>https://www.moogparts.com/parts-matter/Whats-Inside-a-Socket-Style-Part.html</t>
   </si>
   <si>
+    <t>parts-matter/why-are-my-tires-wearing-unevenly.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/why-are-my-tires-wearing-unevenly</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:27:55.995Z</t>
+  </si>
+  <si>
+    <t>Uneven Tire Wear: Causes &amp; Symptoms | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/why-are-my-tires-wearing-unevenly.html</t>
+  </si>
+  <si>
+    <t>parts-matter/why-does-my-steering-feel-loose.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/why-does-my-steering-feel-loose</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:28:03.349Z</t>
+  </si>
+  <si>
+    <t>Loose Steering: Causes &amp; Symptoms | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/why-does-my-steering-feel-loose.html</t>
+  </si>
+  <si>
+    <t>parts-matter/why-is-my-car-vibrating.report.json</t>
+  </si>
+  <si>
+    <t>parts-matter/why-is-my-car-vibrating</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:28:09.937Z</t>
+  </si>
+  <si>
+    <t>Why is My Car Vibrating? | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/parts-matter/why-is-my-car-vibrating.html</t>
+  </si>
+  <si>
     <t>technical/bulletins.report.json</t>
   </si>
   <si>
@@ -904,9 +1417,6 @@
     <t>technical/bulletins/tech-tips.report.json</t>
   </si>
   <si>
-    <t>["hero-overlay","cards-article"]</t>
-  </si>
-  <si>
     <t>technical/bulletins/tech-tips</t>
   </si>
   <si>
@@ -1256,6 +1766,693 @@
   </si>
   <si>
     <t>https://www.moogparts.com/parts/wheel-end/hub-assemblies/premium-hub-assemblies.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/avoiding-sway-bar-link-damage-due-to-overtightening.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/avoiding-sway-bar-link-damage-due-to-overtightening</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:29:41.031Z</t>
+  </si>
+  <si>
+    <t>Avoiding Sway Bar Link Damage | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/avoiding-sway-bar-link-damage-due-to-overtightening.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/ball-joint-installation-tips.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/ball-joint-installation-tips</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:29:49.547Z</t>
+  </si>
+  <si>
+    <t>Avoiding Memory Steer | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/ball-joint-installation-tips.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/checking-stud-taper-fitment-chassis-parts.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/checking-stud-taper-fitment-chassis-parts</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:29:56.814Z</t>
+  </si>
+  <si>
+    <t>Preventing Chassis Part Taper Wear | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/checking-stud-taper-fitment-chassis-parts.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/elliptical-opening-press-in-ball-joint-installation-tip.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/elliptical-opening-press-in-ball-joint-installation-tip</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:30:05.797Z</t>
+  </si>
+  <si>
+    <t>Press-In Ball Joint Tip | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/elliptical-opening-press-in-ball-joint-installation-tip.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/finding-the-right-replacement-u-joint.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/finding-the-right-replacement-u-joint</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:30:13.109Z</t>
+  </si>
+  <si>
+    <t>Finding the Right Replacement U-Joint | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/finding-the-right-replacement-u-joint.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/getting-the-right-ball-joint-for-2014-2016-chevrolet-silverado-and-gmc-sierra-1500-trucks.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/getting-the-right-ball-joint-for-2014-2016-chevrolet-silverado-and-gmc-sierra-1500-trucks</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:30:20.071Z</t>
+  </si>
+  <si>
+    <t>Ball Joints for 2014-16 Silverado-Sierra 1500 | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/getting-the-right-ball-Joint-for-2014-2016-chevrolet-silverado-and-gmc-sierra-1500-trucks.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/getting-the-right-replacement-universal-joint.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/getting-the-right-replacement-universal-joint</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:28:30.842Z</t>
+  </si>
+  <si>
+    <t>Finding the Right U-Joint | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/Getting-the-Right-Replacement-Universal-Joint.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/gm-1500-ball-joint-and-control-arm-fitment.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/gm-1500-ball-joint-and-control-arm-fitment</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:30:26.870Z</t>
+  </si>
+  <si>
+    <t>GM 1500 Ball Joint &amp; Control Arm Fitment | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/gm-1500-ball-joint-and-control-arm-fitment.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/grease-requirements-for-steering-suspension-parts.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/grease-requirements-for-steering-suspension-parts</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:30:34.771Z</t>
+  </si>
+  <si>
+    <t>How to Grease Steering &amp; Suspension Parts | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/grease-requirements-for-steering-suspension-parts.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/greasing-hard-to-access-chassis-parts.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/greasing-hard-to-access-chassis-parts</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:30:40.692Z</t>
+  </si>
+  <si>
+    <t>Greasing Hard-to-Access Chassis Parts | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/greasing-hard-to-access-chassis-parts.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-adjust-camber-and-caster-on-non-adjustable-vehicles.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-adjust-camber-and-caster-on-non-adjustable-vehicles</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:28:36.848Z</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/How-to-Adjust-Camber-and-Caster-on-Non-Adjustable-Vehicles.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-avoid-steering-knuckle-damage-from-overtightening.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-avoid-steering-knuckle-damage-from-overtightening</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:30:47.294Z</t>
+  </si>
+  <si>
+    <t>Ball Joint Tightening Tip | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/how-to-avoid-steering-knuckle-damage-from-overtightening.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-get-the-right-front-hub-assembly-for-2007-chevy-and-gmc-trucks.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-get-the-right-front-hub-assembly-for-2007-chevy-and-gmc-trucks</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:28:45.187Z</t>
+  </si>
+  <si>
+    <t>How to Get the Right Front Hub Assembly for 2007 Chevy &amp; GMC Trucks</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/How-to-Get-the-Right-Front-Hub-Assembly-for-2007-Chevy-and-GMC-Trucks.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-inspect-ball-joints-for-looseness.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-inspect-ball-joints-for-looseness</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:30:54.698Z</t>
+  </si>
+  <si>
+    <t>Signs of Loose Ball Joints | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/how-to-inspect-ball-joints-for-looseness.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-install-a-cotter-pin-on-a-castle-nut.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-install-a-cotter-pin-on-a-castle-nut</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:28:53.187Z</t>
+  </si>
+  <si>
+    <t>Installing Cotter Pin on Castle Nut | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/How-to-Install-a-Cotter-Pin-on-a-Castle-Nut.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-install-a-hub-assembly.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-install-a-hub-assembly</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:29:01.513Z</t>
+  </si>
+  <si>
+    <t>How to Install a Hub Assembly | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/How-to-Install-a-Hub-Assembly.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-install-dust-boot-on-ball-joint.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-install-dust-boot-on-ball-joint</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:31:01.321Z</t>
+  </si>
+  <si>
+    <t>Ball Joint Dust Boot Installation | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/how-to-install-dust-boot-on-ball-joint.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-install-self-locking-nut-on-ball-joint-with-tapered-stud.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-install-self-locking-nut-on-ball-joint-with-tapered-stud</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:31:09.186Z</t>
+  </si>
+  <si>
+    <t>Installing Self-Locking Ball Joint Nut | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/how-to-install-self-locking-nut-on-ball-joint-with-tapered-stud.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-isolate-suspension-noises.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-isolate-suspension-noises</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:29:08.961Z</t>
+  </si>
+  <si>
+    <t>How to Isolate Suspension Noises</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/How-to-Isolate-Suspension-Noises.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-properly-tighten-axle-nut-on-wheel-hub-bearing.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-properly-tighten-axle-nut-on-wheel-hub-bearing</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:31:16.901Z</t>
+  </si>
+  <si>
+    <t>Hub Assembly Tip | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/how-to-properly-tighten-axle-nut-on-wheel-hub-bearing.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-remove-and-install-a-cv-axle.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-remove-and-install-a-cv-axle</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:31:24.300Z</t>
+  </si>
+  <si>
+    <t>CV Axle Replacement | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/how-to-remove-and-install-a-cv-axle.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-replace-lower-ball-joint-with-insert-over-stud.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-replace-lower-ball-joint-with-insert-over-stud</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:31:31.130Z</t>
+  </si>
+  <si>
+    <t>How to Replace Lower Ball Joint with Insert Over Stud | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/how-to-replace-lower-ball-joint-with-insert-over-stud.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-test-ball-joints-for-movement-dodge-ram-jeep.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-test-ball-joints-for-movement-dodge-ram-jeep</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:31:39.667Z</t>
+  </si>
+  <si>
+    <t>Measuring Ball Joint Movement | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/how-to-test-ball-joints-for-movement-dodge-ram-jeep.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-torque-rubber-suspension-bushings.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-torque-rubber-suspension-bushings</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:31:48.239Z</t>
+  </si>
+  <si>
+    <t>Rubber Bushing Torquing Tip | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/how-to-torque-rubber-suspension-bushings.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-torque-stud-nut-on-ball-joint.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/how-to-torque-stud-nut-on-ball-joint</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:31:55.824Z</t>
+  </si>
+  <si>
+    <t>Torquing Ball Joint Stud Nut | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/how-to-torque-stud-nut-on-ball-joint.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/importance-of-proper-torquing-for-aluminum-suspension-parts.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/importance-of-proper-torquing-for-aluminum-suspension-parts</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:32:02.649Z</t>
+  </si>
+  <si>
+    <t>Proper Torquing for Aluminum Chassis Part | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/importance-of-proper-torquing-for-aluminum-suspension-parts.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/installing-servicing-moog-universal-joints.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/installing-servicing-moog-universal-joints</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:32:09.522Z</t>
+  </si>
+  <si>
+    <t>Universal Joint Installation Tips | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/installing-servicing-moog-universal-joints.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/pinch-bolt-style-ball-joint-installation-tip.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/pinch-bolt-style-ball-joint-installation-tip</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:32:17.042Z</t>
+  </si>
+  <si>
+    <t>How to Install Pinch Bolt Ball Joint | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/pinch-bolt-style-ball-joint-installation-tip.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/resolving-error-codes-after-hub-replacement-subaru.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/resolving-error-codes-after-hub-replacement-subaru</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:32:24.100Z</t>
+  </si>
+  <si>
+    <t>Hub Replacement on Subaru SUVs | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/resolving-error-codes-after-hub-replacement-subaru.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/resolving-parking-brake-spring-clearance-issues-ford-lincoln-mercury.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/resolving-parking-brake-spring-clearance-issues-ford-lincoln-mercury</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:32:31.758Z</t>
+  </si>
+  <si>
+    <t>Complete Knuckle Assembly for Ford SUVs | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/resolving-parking-brake-spring-clearance-issues-ford-lincoln-mercury.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/resolving-upper-ball-joint-failure-dodge-ram-trucks.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/resolving-upper-ball-joint-failure-dodge-ram-trucks</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:32:39.771Z</t>
+  </si>
+  <si>
+    <t>Resolving Dodge Ram Trucks Upper Ball Joint Failure | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/resolving-upper-ball-joint-failure-dodge-ram-trucks.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/restoring-handling-with-moog-solid-sway-bar-kit.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/restoring-handling-with-moog-solid-sway-bar-kit</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:32:48.180Z</t>
+  </si>
+  <si>
+    <t>Restoring Handling with MOOG Solid Sway Bar Kit | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/restoring-handling-with-moog-solid-sway-bar-kit.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/selecting-right-tie-rod-ford-super-duty-trucks.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/selecting-right-tie-rod-ford-super-duty-trucks</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:32:55.031Z</t>
+  </si>
+  <si>
+    <t>Tie Rods for Ford Super Duty Trucks | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/selecting-right-tie-rod-ford-super-duty-trucks.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/selecting-the-correct-control-arm-for-2014-2020-chevrolet-silverado-and-gmc-sierra-1500-trucks.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/selecting-the-correct-control-arm-for-2014-2020-chevrolet-silverado-and-gmc-sierra-1500-trucks</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:29:16.009Z</t>
+  </si>
+  <si>
+    <t>Control Arms for Silverado/Sierra 1500 | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/Selecting-the-Correct-Control-Arm-for-2014-2020-Chevrolet-Silverado-and-GMC-Sierra-1500-Trucks.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/solving-center-link-bushing-wear-on-chevy-hd-trucks.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/solving-center-link-bushing-wear-on-chevy-hd-trucks</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:33:01.465Z</t>
+  </si>
+  <si>
+    <t>Solving Center Link Bushing Wear | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/solving-center-link-bushing-wear-on-chevy-hd-trucks.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/solving-memory-steer-ford-ram.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/solving-memory-steer-ford-ram</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:33:08.861Z</t>
+  </si>
+  <si>
+    <t>Memory Steer After Ball Joint Install | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/solving-memory-steer-ford-ram.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/solving-premature-outer-tie-rod-failure-ford-fusion-lincoln-mkz.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/solving-premature-outer-tie-rod-failure-ford-fusion-lincoln-mkz</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:33:16.437Z</t>
+  </si>
+  <si>
+    <t>Solving Premature Outer Tie Rod Failure | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/solving-premature-outer-tie-rod-failure-ford-fusion-lincoln-mkz.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/tie-rod-installation-tips.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/tie-rod-installation-tips</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:33:25.202Z</t>
+  </si>
+  <si>
+    <t>Installing Tie Rods | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/tie-rod-installation-tips.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/tip-for-installing-ball-joints-on-subaru-applications.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/tip-for-installing-ball-joints-on-subaru-applications</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:33:33.121Z</t>
+  </si>
+  <si>
+    <t>Subaru Ball Joint Tip | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/tip-for-installing-ball-joints-on-subaru-applications.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/tips-for-replacing-a-cv-axle.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/tips-for-replacing-a-cv-axle</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:33:39.833Z</t>
+  </si>
+  <si>
+    <t>Replacing a CV Axle | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/tips-for-replacing-a-cv-axle.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/track-bar-ball-joint-solves-front-end-shimmy.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/track-bar-ball-joint-solves-front-end-shimmy</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:33:47.172Z</t>
+  </si>
+  <si>
+    <t>Track Bar Ball Joint Solves Front End Shimmy | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/track-bar-ball-joint-solves-front-end-shimmy.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/troubleshooting-vertical-control-arm-bushing-failure.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/troubleshooting-vertical-control-arm-bushing-failure</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:33:55.164Z</t>
+  </si>
+  <si>
+    <t>Troubleshooting Vertical Control Arm Bushing Failure | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/troubleshooting-vertical-control-arm-bushing-failure.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/u-joints-for-2013-2018-ram-2500-3500-with-cummins-6-7l-engine.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/u-joints-for-2013-2018-ram-2500-3500-with-cummins-6-7l-engine</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:29:23.523Z</t>
+  </si>
+  <si>
+    <t>Ram 2500/3500 U-Joints | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/U-Joints-for-2013-2018-Ram-2500-3500-with-Cummins-6-7L-Engine.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/using-proper-stud-fasteners-for-ball-joint-tie-rod-end-repairs.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/using-proper-stud-fasteners-for-ball-joint-tie-rod-end-repairs</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:34:01.697Z</t>
+  </si>
+  <si>
+    <t>Ball Joint &amp; Tie Rod Fasteners | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/using-proper-stud-fasteners-for-ball-joint-tie-rod-end-repairs.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/when-to-use-a-moog-oversized-ball-joint.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/when-to-use-a-moog-oversized-ball-joint</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:34:11.322Z</t>
+  </si>
+  <si>
+    <t>Do I Need Oversized Ball Joints? | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/when-to-use-a-moog-oversized-ball-joint.html</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/why-an-alignment-is-needed-after-an-outer-tie-rod-replacement.report.json</t>
+  </si>
+  <si>
+    <t>technical/bulletins/tech-tips/why-an-alignment-is-needed-after-an-outer-tie-rod-replacement</t>
+  </si>
+  <si>
+    <t>2026-06-29T03:29:32.945Z</t>
+  </si>
+  <si>
+    <t>Alignment &amp; Outer Tie Rods | MOOG Parts</t>
+  </si>
+  <si>
+    <t>https://www.moogparts.com/technical/bulletins/tech-tips/Why-an-Alignment-is-Needed-After-an-Outer-Tie-Rod-Replacement.html</t>
   </si>
 </sst>
 </file>
@@ -1644,7 +2841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -1840,146 +3037,146 @@
         <v>46</v>
       </c>
       <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
         <v>47</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
         <v>48</v>
       </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>49</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>50</v>
-      </c>
-      <c r="H8" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
         <v>52</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>53</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
         <v>54</v>
       </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>55</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>56</v>
-      </c>
-      <c r="G9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H9" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
         <v>59</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
         <v>60</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
         <v>61</v>
       </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>62</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>63</v>
-      </c>
-      <c r="G10" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
         <v>66</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
         <v>67</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>68</v>
       </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>69</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>70</v>
-      </c>
-      <c r="G11" t="s">
-        <v>71</v>
-      </c>
-      <c r="H11" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" t="s">
         <v>73</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
         <v>74</v>
       </c>
-      <c r="C12" t="s">
+      <c r="F12" t="s">
         <v>75</v>
       </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>76</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>77</v>
-      </c>
-      <c r="H12" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
         <v>79</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>80</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
         <v>81</v>
-      </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" t="s">
-        <v>12</v>
       </c>
       <c r="F13" t="s">
         <v>82</v>
@@ -2005,1602 +3202,3682 @@
         <v>11</v>
       </c>
       <c r="E14" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" t="s">
         <v>88</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>89</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>90</v>
-      </c>
-      <c r="H14" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" t="s">
         <v>92</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>93</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
         <v>94</v>
       </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>95</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>96</v>
-      </c>
-      <c r="H15" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
         <v>98</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" t="s">
         <v>99</v>
       </c>
-      <c r="C16" t="s">
+      <c r="G16" t="s">
         <v>100</v>
       </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>101</v>
-      </c>
-      <c r="G16" t="s">
-        <v>102</v>
-      </c>
-      <c r="H16" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" t="s">
         <v>104</v>
       </c>
-      <c r="B17" t="s">
+      <c r="G17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" t="s">
         <v>105</v>
-      </c>
-      <c r="C17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" t="s">
-        <v>88</v>
-      </c>
-      <c r="F17" t="s">
-        <v>107</v>
-      </c>
-      <c r="G17" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" t="s">
         <v>110</v>
-      </c>
-      <c r="B18" t="s">
-        <v>111</v>
-      </c>
-      <c r="C18" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" t="s">
-        <v>114</v>
-      </c>
-      <c r="G18" t="s">
-        <v>115</v>
-      </c>
-      <c r="H18" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" t="s">
         <v>113</v>
       </c>
-      <c r="F19" t="s">
-        <v>119</v>
-      </c>
       <c r="G19" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="H19" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="G20" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H20" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F21" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G21" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H21" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F22" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G22" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H22" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F23" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G23" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H23" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F24" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G24" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H24" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F25" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G25" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H25" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G26" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H26" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B27" t="s">
-        <v>158</v>
+        <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="F27" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G27" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="H27" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C28" t="s">
+        <v>159</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>160</v>
+      </c>
+      <c r="F28" t="s">
+        <v>161</v>
+      </c>
+      <c r="G28" t="s">
+        <v>162</v>
+      </c>
+      <c r="H28" t="s">
         <v>163</v>
-      </c>
-      <c r="B28" t="s">
-        <v>164</v>
-      </c>
-      <c r="C28" t="s">
-        <v>165</v>
-      </c>
-      <c r="D28" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" t="s">
-        <v>69</v>
-      </c>
-      <c r="F28" t="s">
-        <v>166</v>
-      </c>
-      <c r="G28" t="s">
-        <v>167</v>
-      </c>
-      <c r="H28" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>164</v>
+      </c>
+      <c r="B29" t="s">
+        <v>165</v>
+      </c>
+      <c r="C29" t="s">
+        <v>166</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29" t="s">
+        <v>167</v>
+      </c>
+      <c r="G29" t="s">
+        <v>168</v>
+      </c>
+      <c r="H29" t="s">
         <v>169</v>
-      </c>
-      <c r="B29" t="s">
-        <v>170</v>
-      </c>
-      <c r="C29" t="s">
-        <v>171</v>
-      </c>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" t="s">
-        <v>113</v>
-      </c>
-      <c r="F29" t="s">
-        <v>172</v>
-      </c>
-      <c r="G29" t="s">
-        <v>173</v>
-      </c>
-      <c r="H29" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>170</v>
+      </c>
+      <c r="B30" t="s">
+        <v>171</v>
+      </c>
+      <c r="C30" t="s">
+        <v>172</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>160</v>
+      </c>
+      <c r="F30" t="s">
+        <v>173</v>
+      </c>
+      <c r="G30" t="s">
+        <v>174</v>
+      </c>
+      <c r="H30" t="s">
         <v>175</v>
-      </c>
-      <c r="B30" t="s">
-        <v>164</v>
-      </c>
-      <c r="C30" t="s">
-        <v>176</v>
-      </c>
-      <c r="D30" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" t="s">
-        <v>69</v>
-      </c>
-      <c r="F30" t="s">
-        <v>177</v>
-      </c>
-      <c r="G30" t="s">
-        <v>178</v>
-      </c>
-      <c r="H30" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31" t="s">
+        <v>177</v>
+      </c>
+      <c r="C31" t="s">
+        <v>178</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>160</v>
+      </c>
+      <c r="F31" t="s">
+        <v>179</v>
+      </c>
+      <c r="G31" t="s">
         <v>180</v>
       </c>
-      <c r="B31" t="s">
-        <v>111</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="H31" t="s">
         <v>181</v>
-      </c>
-      <c r="D31" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" t="s">
-        <v>182</v>
-      </c>
-      <c r="F31" t="s">
-        <v>183</v>
-      </c>
-      <c r="G31" t="s">
-        <v>184</v>
-      </c>
-      <c r="H31" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>182</v>
+      </c>
+      <c r="B32" t="s">
+        <v>183</v>
+      </c>
+      <c r="C32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>123</v>
+      </c>
+      <c r="F32" t="s">
+        <v>185</v>
+      </c>
+      <c r="G32" t="s">
         <v>186</v>
       </c>
-      <c r="B32" t="s">
+      <c r="H32" t="s">
         <v>187</v>
-      </c>
-      <c r="C32" t="s">
-        <v>188</v>
-      </c>
-      <c r="D32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" t="s">
-        <v>182</v>
-      </c>
-      <c r="F32" t="s">
-        <v>189</v>
-      </c>
-      <c r="G32" t="s">
-        <v>190</v>
-      </c>
-      <c r="H32" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>188</v>
+      </c>
+      <c r="B33" t="s">
+        <v>183</v>
+      </c>
+      <c r="C33" t="s">
+        <v>189</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>123</v>
+      </c>
+      <c r="F33" t="s">
+        <v>190</v>
+      </c>
+      <c r="G33" t="s">
+        <v>191</v>
+      </c>
+      <c r="H33" t="s">
         <v>192</v>
-      </c>
-      <c r="B33" t="s">
-        <v>193</v>
-      </c>
-      <c r="C33" t="s">
-        <v>194</v>
-      </c>
-      <c r="D33" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" t="s">
-        <v>182</v>
-      </c>
-      <c r="F33" t="s">
-        <v>195</v>
-      </c>
-      <c r="G33" t="s">
-        <v>196</v>
-      </c>
-      <c r="H33" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B34" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="C34" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="F34" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G34" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="H34" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B35" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C35" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
       </c>
       <c r="E35" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="F35" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G35" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="H35" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B36" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C36" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="F36" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G36" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H36" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B37" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C37" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="F37" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G37" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H37" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B38" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C38" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="F38" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G38" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H38" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B39" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C39" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="F39" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G39" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H39" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B40" t="s">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="C40" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
       </c>
       <c r="E40" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="F40" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="G40" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="H40" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>183</v>
       </c>
       <c r="C41" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="F41" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G41" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H41" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B42" t="s">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="C42" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="F42" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G42" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="H42" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B43" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C43" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="F43" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="G43" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="H43" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B44" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C44" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="F44" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="G44" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="H44" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B45" t="s">
-        <v>256</v>
+        <v>183</v>
       </c>
       <c r="C45" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="F45" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="G45" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="H45" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B46" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
       </c>
       <c r="E46" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="F46" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="G46" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="H46" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
+        <v>183</v>
       </c>
       <c r="C47" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="F47" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="G47" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="H47" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B48" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C48" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
       </c>
       <c r="E48" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="F48" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="G48" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="H48" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B49" t="s">
-        <v>86</v>
+        <v>183</v>
       </c>
       <c r="C49" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
       </c>
       <c r="E49" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="F49" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="G49" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H49" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B50" t="s">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="C50" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
       </c>
       <c r="E50" t="s">
-        <v>283</v>
+        <v>123</v>
       </c>
       <c r="F50" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="G50" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="H50" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>183</v>
       </c>
       <c r="C51" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
       </c>
       <c r="E51" t="s">
-        <v>283</v>
+        <v>123</v>
       </c>
       <c r="F51" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="G51" t="s">
-        <v>44</v>
+        <v>281</v>
       </c>
       <c r="H51" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B52" t="s">
-        <v>41</v>
+        <v>183</v>
       </c>
       <c r="C52" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>283</v>
+        <v>123</v>
       </c>
       <c r="F52" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="G52" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="H52" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B53" t="s">
-        <v>297</v>
+        <v>183</v>
       </c>
       <c r="C53" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
       </c>
       <c r="E53" t="s">
-        <v>299</v>
+        <v>123</v>
       </c>
       <c r="F53" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="G53" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="H53" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="B54" t="s">
-        <v>41</v>
+        <v>183</v>
       </c>
       <c r="C54" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
       </c>
       <c r="E54" t="s">
-        <v>283</v>
+        <v>123</v>
       </c>
       <c r="F54" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="G54" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="H54" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B55" t="s">
-        <v>41</v>
+        <v>183</v>
       </c>
       <c r="C55" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
       </c>
       <c r="E55" t="s">
-        <v>283</v>
+        <v>123</v>
       </c>
       <c r="F55" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G55" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="H55" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="B56" t="s">
-        <v>314</v>
+        <v>183</v>
       </c>
       <c r="C56" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
       </c>
       <c r="E56" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F56" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="G56" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="H56" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="B57" t="s">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="C57" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
       </c>
       <c r="E57" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F57" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="G57" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="H57" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="B58" t="s">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="C58" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
       </c>
       <c r="E58" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F58" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="G58" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="H58" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="B59" t="s">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="C59" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F59" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="G59" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="H59" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="B60" t="s">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="C60" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F60" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="G60" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="H60" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="B61" t="s">
-        <v>193</v>
+        <v>329</v>
       </c>
       <c r="C61" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
       </c>
       <c r="E61" t="s">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="F61" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="G61" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="H61" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="B62" t="s">
-        <v>193</v>
+        <v>335</v>
       </c>
       <c r="C62" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
       </c>
       <c r="E62" t="s">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="F62" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="G62" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="H62" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B63" t="s">
-        <v>193</v>
+        <v>341</v>
       </c>
       <c r="C63" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
       </c>
       <c r="E63" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="F63" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="G63" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="H63" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B64" t="s">
-        <v>193</v>
+        <v>335</v>
       </c>
       <c r="C64" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="F64" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="G64" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="H64" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B65" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C65" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>182</v>
+        <v>353</v>
       </c>
       <c r="F65" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="G65" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="H65" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B66" t="s">
-        <v>193</v>
+        <v>358</v>
       </c>
       <c r="C66" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
       </c>
       <c r="E66" t="s">
-        <v>182</v>
+        <v>353</v>
       </c>
       <c r="F66" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="G66" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="H66" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B67" t="s">
-        <v>193</v>
+        <v>364</v>
       </c>
       <c r="C67" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
       </c>
       <c r="E67" t="s">
-        <v>182</v>
+        <v>353</v>
       </c>
       <c r="F67" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G67" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="H67" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>369</v>
+      </c>
+      <c r="B68" t="s">
+        <v>370</v>
+      </c>
+      <c r="C68" t="s">
+        <v>371</v>
+      </c>
+      <c r="D68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" t="s">
+        <v>160</v>
+      </c>
+      <c r="F68" t="s">
+        <v>372</v>
+      </c>
+      <c r="G68" t="s">
+        <v>373</v>
+      </c>
+      <c r="H68" t="s">
         <v>374</v>
-      </c>
-      <c r="B68" t="s">
-        <v>193</v>
-      </c>
-      <c r="C68" t="s">
-        <v>375</v>
-      </c>
-      <c r="D68" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" t="s">
-        <v>182</v>
-      </c>
-      <c r="F68" t="s">
-        <v>376</v>
-      </c>
-      <c r="G68" t="s">
-        <v>377</v>
-      </c>
-      <c r="H68" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>375</v>
+      </c>
+      <c r="B69" t="s">
+        <v>364</v>
+      </c>
+      <c r="C69" t="s">
+        <v>376</v>
+      </c>
+      <c r="D69" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" t="s">
+        <v>353</v>
+      </c>
+      <c r="F69" t="s">
+        <v>377</v>
+      </c>
+      <c r="G69" t="s">
+        <v>378</v>
+      </c>
+      <c r="H69" t="s">
         <v>379</v>
-      </c>
-      <c r="B69" t="s">
-        <v>193</v>
-      </c>
-      <c r="C69" t="s">
-        <v>380</v>
-      </c>
-      <c r="D69" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" t="s">
-        <v>182</v>
-      </c>
-      <c r="F69" t="s">
-        <v>381</v>
-      </c>
-      <c r="G69" t="s">
-        <v>382</v>
-      </c>
-      <c r="H69" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>380</v>
+      </c>
+      <c r="B70" t="s">
+        <v>364</v>
+      </c>
+      <c r="C70" t="s">
+        <v>381</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" t="s">
+        <v>353</v>
+      </c>
+      <c r="F70" t="s">
+        <v>382</v>
+      </c>
+      <c r="G70" t="s">
+        <v>383</v>
+      </c>
+      <c r="H70" t="s">
         <v>384</v>
-      </c>
-      <c r="B70" t="s">
-        <v>193</v>
-      </c>
-      <c r="C70" t="s">
-        <v>385</v>
-      </c>
-      <c r="D70" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" t="s">
-        <v>182</v>
-      </c>
-      <c r="F70" t="s">
-        <v>386</v>
-      </c>
-      <c r="G70" t="s">
-        <v>387</v>
-      </c>
-      <c r="H70" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>385</v>
+      </c>
+      <c r="B71" t="s">
+        <v>364</v>
+      </c>
+      <c r="C71" t="s">
+        <v>386</v>
+      </c>
+      <c r="D71" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" t="s">
+        <v>353</v>
+      </c>
+      <c r="F71" t="s">
+        <v>387</v>
+      </c>
+      <c r="G71" t="s">
+        <v>388</v>
+      </c>
+      <c r="H71" t="s">
         <v>389</v>
-      </c>
-      <c r="B71" t="s">
-        <v>390</v>
-      </c>
-      <c r="C71" t="s">
-        <v>391</v>
-      </c>
-      <c r="D71" t="s">
-        <v>11</v>
-      </c>
-      <c r="E71" t="s">
-        <v>182</v>
-      </c>
-      <c r="F71" t="s">
-        <v>392</v>
-      </c>
-      <c r="G71" t="s">
-        <v>393</v>
-      </c>
-      <c r="H71" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B72" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="C72" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="D72" t="s">
         <v>11</v>
       </c>
       <c r="E72" t="s">
-        <v>182</v>
+        <v>353</v>
       </c>
       <c r="F72" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="G72" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="H72" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B73" t="s">
-        <v>230</v>
+        <v>364</v>
       </c>
       <c r="C73" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
       </c>
       <c r="E73" t="s">
-        <v>182</v>
+        <v>353</v>
       </c>
       <c r="F73" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="G73" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H73" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>400</v>
+      </c>
+      <c r="B74" t="s">
+        <v>401</v>
+      </c>
+      <c r="C74" t="s">
+        <v>402</v>
+      </c>
+      <c r="D74" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" t="s">
+        <v>353</v>
+      </c>
+      <c r="F74" t="s">
+        <v>403</v>
+      </c>
+      <c r="G74" t="s">
+        <v>404</v>
+      </c>
+      <c r="H74" t="s">
         <v>405</v>
-      </c>
-      <c r="B74" t="s">
-        <v>230</v>
-      </c>
-      <c r="C74" t="s">
-        <v>406</v>
-      </c>
-      <c r="D74" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" t="s">
-        <v>182</v>
-      </c>
-      <c r="F74" t="s">
-        <v>407</v>
-      </c>
-      <c r="G74" t="s">
-        <v>408</v>
-      </c>
-      <c r="H74" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>406</v>
+      </c>
+      <c r="B75" t="s">
+        <v>165</v>
+      </c>
+      <c r="C75" t="s">
+        <v>407</v>
+      </c>
+      <c r="D75" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" t="s">
+        <v>160</v>
+      </c>
+      <c r="F75" t="s">
+        <v>408</v>
+      </c>
+      <c r="G75" t="s">
+        <v>409</v>
+      </c>
+      <c r="H75" t="s">
         <v>410</v>
       </c>
-      <c r="B75" t="s">
-        <v>230</v>
-      </c>
-      <c r="C75" t="s">
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>411</v>
       </c>
-      <c r="D75" t="s">
-        <v>11</v>
-      </c>
-      <c r="E75" t="s">
-        <v>182</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="B76" t="s">
+        <v>401</v>
+      </c>
+      <c r="C76" t="s">
         <v>412</v>
       </c>
-      <c r="G75" t="s">
+      <c r="D76" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" t="s">
+        <v>353</v>
+      </c>
+      <c r="F76" t="s">
         <v>413</v>
       </c>
-      <c r="H75" t="s">
+      <c r="G76" t="s">
         <v>414</v>
+      </c>
+      <c r="H76" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>416</v>
+      </c>
+      <c r="B77" t="s">
+        <v>364</v>
+      </c>
+      <c r="C77" t="s">
+        <v>417</v>
+      </c>
+      <c r="D77" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" t="s">
+        <v>353</v>
+      </c>
+      <c r="F77" t="s">
+        <v>418</v>
+      </c>
+      <c r="G77" t="s">
+        <v>419</v>
+      </c>
+      <c r="H77" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>421</v>
+      </c>
+      <c r="B78" t="s">
+        <v>358</v>
+      </c>
+      <c r="C78" t="s">
+        <v>422</v>
+      </c>
+      <c r="D78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" t="s">
+        <v>353</v>
+      </c>
+      <c r="F78" t="s">
+        <v>423</v>
+      </c>
+      <c r="G78" t="s">
+        <v>424</v>
+      </c>
+      <c r="H78" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>426</v>
+      </c>
+      <c r="B79" t="s">
+        <v>427</v>
+      </c>
+      <c r="C79" t="s">
+        <v>428</v>
+      </c>
+      <c r="D79" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" t="s">
+        <v>353</v>
+      </c>
+      <c r="F79" t="s">
+        <v>429</v>
+      </c>
+      <c r="G79" t="s">
+        <v>430</v>
+      </c>
+      <c r="H79" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>432</v>
+      </c>
+      <c r="B80" t="s">
+        <v>364</v>
+      </c>
+      <c r="C80" t="s">
+        <v>433</v>
+      </c>
+      <c r="D80" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" t="s">
+        <v>353</v>
+      </c>
+      <c r="F80" t="s">
+        <v>434</v>
+      </c>
+      <c r="G80" t="s">
+        <v>435</v>
+      </c>
+      <c r="H80" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>437</v>
+      </c>
+      <c r="B81" t="s">
+        <v>177</v>
+      </c>
+      <c r="C81" t="s">
+        <v>438</v>
+      </c>
+      <c r="D81" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" t="s">
+        <v>160</v>
+      </c>
+      <c r="F81" t="s">
+        <v>439</v>
+      </c>
+      <c r="G81" t="s">
+        <v>440</v>
+      </c>
+      <c r="H81" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>442</v>
+      </c>
+      <c r="B82" t="s">
+        <v>364</v>
+      </c>
+      <c r="C82" t="s">
+        <v>443</v>
+      </c>
+      <c r="D82" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" t="s">
+        <v>353</v>
+      </c>
+      <c r="F82" t="s">
+        <v>444</v>
+      </c>
+      <c r="G82" t="s">
+        <v>445</v>
+      </c>
+      <c r="H82" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>447</v>
+      </c>
+      <c r="B83" t="s">
+        <v>158</v>
+      </c>
+      <c r="C83" t="s">
+        <v>448</v>
+      </c>
+      <c r="D83" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" t="s">
+        <v>160</v>
+      </c>
+      <c r="F83" t="s">
+        <v>449</v>
+      </c>
+      <c r="G83" t="s">
+        <v>450</v>
+      </c>
+      <c r="H83" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>452</v>
+      </c>
+      <c r="B84" t="s">
+        <v>92</v>
+      </c>
+      <c r="C84" t="s">
+        <v>453</v>
+      </c>
+      <c r="D84" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" t="s">
+        <v>454</v>
+      </c>
+      <c r="F84" t="s">
+        <v>455</v>
+      </c>
+      <c r="G84" t="s">
+        <v>456</v>
+      </c>
+      <c r="H84" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>458</v>
+      </c>
+      <c r="B85" t="s">
+        <v>41</v>
+      </c>
+      <c r="C85" t="s">
+        <v>459</v>
+      </c>
+      <c r="D85" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" t="s">
+        <v>454</v>
+      </c>
+      <c r="F85" t="s">
+        <v>460</v>
+      </c>
+      <c r="G85" t="s">
+        <v>44</v>
+      </c>
+      <c r="H85" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>462</v>
+      </c>
+      <c r="B86" t="s">
+        <v>41</v>
+      </c>
+      <c r="C86" t="s">
+        <v>463</v>
+      </c>
+      <c r="D86" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" t="s">
+        <v>454</v>
+      </c>
+      <c r="F86" t="s">
+        <v>464</v>
+      </c>
+      <c r="G86" t="s">
+        <v>465</v>
+      </c>
+      <c r="H86" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>467</v>
+      </c>
+      <c r="B87" t="s">
+        <v>58</v>
+      </c>
+      <c r="C87" t="s">
+        <v>468</v>
+      </c>
+      <c r="D87" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" t="s">
+        <v>469</v>
+      </c>
+      <c r="F87" t="s">
+        <v>470</v>
+      </c>
+      <c r="G87" t="s">
+        <v>471</v>
+      </c>
+      <c r="H87" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>473</v>
+      </c>
+      <c r="B88" t="s">
+        <v>41</v>
+      </c>
+      <c r="C88" t="s">
+        <v>474</v>
+      </c>
+      <c r="D88" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" t="s">
+        <v>454</v>
+      </c>
+      <c r="F88" t="s">
+        <v>475</v>
+      </c>
+      <c r="G88" t="s">
+        <v>476</v>
+      </c>
+      <c r="H88" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>478</v>
+      </c>
+      <c r="B89" t="s">
+        <v>41</v>
+      </c>
+      <c r="C89" t="s">
+        <v>479</v>
+      </c>
+      <c r="D89" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" t="s">
+        <v>454</v>
+      </c>
+      <c r="F89" t="s">
+        <v>480</v>
+      </c>
+      <c r="G89" t="s">
+        <v>481</v>
+      </c>
+      <c r="H89" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>483</v>
+      </c>
+      <c r="B90" t="s">
+        <v>484</v>
+      </c>
+      <c r="C90" t="s">
+        <v>485</v>
+      </c>
+      <c r="D90" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" t="s">
+        <v>123</v>
+      </c>
+      <c r="F90" t="s">
+        <v>486</v>
+      </c>
+      <c r="G90" t="s">
+        <v>487</v>
+      </c>
+      <c r="H90" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>489</v>
+      </c>
+      <c r="B91" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" t="s">
+        <v>490</v>
+      </c>
+      <c r="D91" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" t="s">
+        <v>123</v>
+      </c>
+      <c r="F91" t="s">
+        <v>491</v>
+      </c>
+      <c r="G91" t="s">
+        <v>492</v>
+      </c>
+      <c r="H91" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>494</v>
+      </c>
+      <c r="B92" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92" t="s">
+        <v>495</v>
+      </c>
+      <c r="D92" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" t="s">
+        <v>123</v>
+      </c>
+      <c r="F92" t="s">
+        <v>496</v>
+      </c>
+      <c r="G92" t="s">
+        <v>497</v>
+      </c>
+      <c r="H92" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>499</v>
+      </c>
+      <c r="B93" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93" t="s">
+        <v>500</v>
+      </c>
+      <c r="D93" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" t="s">
+        <v>123</v>
+      </c>
+      <c r="F93" t="s">
+        <v>501</v>
+      </c>
+      <c r="G93" t="s">
+        <v>502</v>
+      </c>
+      <c r="H93" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>504</v>
+      </c>
+      <c r="B94" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" t="s">
+        <v>505</v>
+      </c>
+      <c r="D94" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" t="s">
+        <v>123</v>
+      </c>
+      <c r="F94" t="s">
+        <v>506</v>
+      </c>
+      <c r="G94" t="s">
+        <v>507</v>
+      </c>
+      <c r="H94" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>509</v>
+      </c>
+      <c r="B95" t="s">
+        <v>364</v>
+      </c>
+      <c r="C95" t="s">
+        <v>510</v>
+      </c>
+      <c r="D95" t="s">
+        <v>11</v>
+      </c>
+      <c r="E95" t="s">
+        <v>353</v>
+      </c>
+      <c r="F95" t="s">
+        <v>511</v>
+      </c>
+      <c r="G95" t="s">
+        <v>512</v>
+      </c>
+      <c r="H95" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>514</v>
+      </c>
+      <c r="B96" t="s">
+        <v>364</v>
+      </c>
+      <c r="C96" t="s">
+        <v>515</v>
+      </c>
+      <c r="D96" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" t="s">
+        <v>353</v>
+      </c>
+      <c r="F96" t="s">
+        <v>516</v>
+      </c>
+      <c r="G96" t="s">
+        <v>517</v>
+      </c>
+      <c r="H96" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>519</v>
+      </c>
+      <c r="B97" t="s">
+        <v>364</v>
+      </c>
+      <c r="C97" t="s">
+        <v>520</v>
+      </c>
+      <c r="D97" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" t="s">
+        <v>353</v>
+      </c>
+      <c r="F97" t="s">
+        <v>521</v>
+      </c>
+      <c r="G97" t="s">
+        <v>522</v>
+      </c>
+      <c r="H97" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>524</v>
+      </c>
+      <c r="B98" t="s">
+        <v>364</v>
+      </c>
+      <c r="C98" t="s">
+        <v>525</v>
+      </c>
+      <c r="D98" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" t="s">
+        <v>353</v>
+      </c>
+      <c r="F98" t="s">
+        <v>526</v>
+      </c>
+      <c r="G98" t="s">
+        <v>527</v>
+      </c>
+      <c r="H98" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>529</v>
+      </c>
+      <c r="B99" t="s">
+        <v>364</v>
+      </c>
+      <c r="C99" t="s">
+        <v>530</v>
+      </c>
+      <c r="D99" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" t="s">
+        <v>353</v>
+      </c>
+      <c r="F99" t="s">
+        <v>531</v>
+      </c>
+      <c r="G99" t="s">
+        <v>532</v>
+      </c>
+      <c r="H99" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>534</v>
+      </c>
+      <c r="B100" t="s">
+        <v>364</v>
+      </c>
+      <c r="C100" t="s">
+        <v>535</v>
+      </c>
+      <c r="D100" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" t="s">
+        <v>353</v>
+      </c>
+      <c r="F100" t="s">
+        <v>536</v>
+      </c>
+      <c r="G100" t="s">
+        <v>537</v>
+      </c>
+      <c r="H100" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>539</v>
+      </c>
+      <c r="B101" t="s">
+        <v>364</v>
+      </c>
+      <c r="C101" t="s">
+        <v>540</v>
+      </c>
+      <c r="D101" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" t="s">
+        <v>353</v>
+      </c>
+      <c r="F101" t="s">
+        <v>541</v>
+      </c>
+      <c r="G101" t="s">
+        <v>542</v>
+      </c>
+      <c r="H101" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>544</v>
+      </c>
+      <c r="B102" t="s">
+        <v>364</v>
+      </c>
+      <c r="C102" t="s">
+        <v>545</v>
+      </c>
+      <c r="D102" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" t="s">
+        <v>353</v>
+      </c>
+      <c r="F102" t="s">
+        <v>546</v>
+      </c>
+      <c r="G102" t="s">
+        <v>547</v>
+      </c>
+      <c r="H102" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>549</v>
+      </c>
+      <c r="B103" t="s">
+        <v>364</v>
+      </c>
+      <c r="C103" t="s">
+        <v>550</v>
+      </c>
+      <c r="D103" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" t="s">
+        <v>353</v>
+      </c>
+      <c r="F103" t="s">
+        <v>551</v>
+      </c>
+      <c r="G103" t="s">
+        <v>552</v>
+      </c>
+      <c r="H103" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>554</v>
+      </c>
+      <c r="B104" t="s">
+        <v>364</v>
+      </c>
+      <c r="C104" t="s">
+        <v>555</v>
+      </c>
+      <c r="D104" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" t="s">
+        <v>353</v>
+      </c>
+      <c r="F104" t="s">
+        <v>556</v>
+      </c>
+      <c r="G104" t="s">
+        <v>557</v>
+      </c>
+      <c r="H104" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>559</v>
+      </c>
+      <c r="B105" t="s">
+        <v>560</v>
+      </c>
+      <c r="C105" t="s">
+        <v>561</v>
+      </c>
+      <c r="D105" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" t="s">
+        <v>353</v>
+      </c>
+      <c r="F105" t="s">
+        <v>562</v>
+      </c>
+      <c r="G105" t="s">
+        <v>563</v>
+      </c>
+      <c r="H105" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>565</v>
+      </c>
+      <c r="B106" t="s">
+        <v>560</v>
+      </c>
+      <c r="C106" t="s">
+        <v>566</v>
+      </c>
+      <c r="D106" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" t="s">
+        <v>353</v>
+      </c>
+      <c r="F106" t="s">
+        <v>567</v>
+      </c>
+      <c r="G106" t="s">
+        <v>568</v>
+      </c>
+      <c r="H106" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>570</v>
+      </c>
+      <c r="B107" t="s">
+        <v>401</v>
+      </c>
+      <c r="C107" t="s">
+        <v>571</v>
+      </c>
+      <c r="D107" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" t="s">
+        <v>353</v>
+      </c>
+      <c r="F107" t="s">
+        <v>572</v>
+      </c>
+      <c r="G107" t="s">
+        <v>573</v>
+      </c>
+      <c r="H107" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>575</v>
+      </c>
+      <c r="B108" t="s">
+        <v>401</v>
+      </c>
+      <c r="C108" t="s">
+        <v>576</v>
+      </c>
+      <c r="D108" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" t="s">
+        <v>353</v>
+      </c>
+      <c r="F108" t="s">
+        <v>577</v>
+      </c>
+      <c r="G108" t="s">
+        <v>578</v>
+      </c>
+      <c r="H108" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>580</v>
+      </c>
+      <c r="B109" t="s">
+        <v>401</v>
+      </c>
+      <c r="C109" t="s">
+        <v>581</v>
+      </c>
+      <c r="D109" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" t="s">
+        <v>353</v>
+      </c>
+      <c r="F109" t="s">
+        <v>582</v>
+      </c>
+      <c r="G109" t="s">
+        <v>583</v>
+      </c>
+      <c r="H109" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>585</v>
+      </c>
+      <c r="B110" t="s">
+        <v>183</v>
+      </c>
+      <c r="C110" t="s">
+        <v>586</v>
+      </c>
+      <c r="D110" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" t="s">
+        <v>123</v>
+      </c>
+      <c r="F110" t="s">
+        <v>587</v>
+      </c>
+      <c r="G110" t="s">
+        <v>588</v>
+      </c>
+      <c r="H110" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>590</v>
+      </c>
+      <c r="B111" t="s">
+        <v>183</v>
+      </c>
+      <c r="C111" t="s">
+        <v>591</v>
+      </c>
+      <c r="D111" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" t="s">
+        <v>123</v>
+      </c>
+      <c r="F111" t="s">
+        <v>592</v>
+      </c>
+      <c r="G111" t="s">
+        <v>593</v>
+      </c>
+      <c r="H111" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>595</v>
+      </c>
+      <c r="B112" t="s">
+        <v>183</v>
+      </c>
+      <c r="C112" t="s">
+        <v>596</v>
+      </c>
+      <c r="D112" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" t="s">
+        <v>123</v>
+      </c>
+      <c r="F112" t="s">
+        <v>597</v>
+      </c>
+      <c r="G112" t="s">
+        <v>598</v>
+      </c>
+      <c r="H112" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>600</v>
+      </c>
+      <c r="B113" t="s">
+        <v>183</v>
+      </c>
+      <c r="C113" t="s">
+        <v>601</v>
+      </c>
+      <c r="D113" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" t="s">
+        <v>123</v>
+      </c>
+      <c r="F113" t="s">
+        <v>602</v>
+      </c>
+      <c r="G113" t="s">
+        <v>603</v>
+      </c>
+      <c r="H113" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>605</v>
+      </c>
+      <c r="B114" t="s">
+        <v>183</v>
+      </c>
+      <c r="C114" t="s">
+        <v>606</v>
+      </c>
+      <c r="D114" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" t="s">
+        <v>123</v>
+      </c>
+      <c r="F114" t="s">
+        <v>607</v>
+      </c>
+      <c r="G114" t="s">
+        <v>608</v>
+      </c>
+      <c r="H114" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>610</v>
+      </c>
+      <c r="B115" t="s">
+        <v>183</v>
+      </c>
+      <c r="C115" t="s">
+        <v>611</v>
+      </c>
+      <c r="D115" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" t="s">
+        <v>123</v>
+      </c>
+      <c r="F115" t="s">
+        <v>612</v>
+      </c>
+      <c r="G115" t="s">
+        <v>613</v>
+      </c>
+      <c r="H115" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>615</v>
+      </c>
+      <c r="B116" t="s">
+        <v>183</v>
+      </c>
+      <c r="C116" t="s">
+        <v>616</v>
+      </c>
+      <c r="D116" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" t="s">
+        <v>123</v>
+      </c>
+      <c r="F116" t="s">
+        <v>617</v>
+      </c>
+      <c r="G116" t="s">
+        <v>618</v>
+      </c>
+      <c r="H116" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>620</v>
+      </c>
+      <c r="B117" t="s">
+        <v>183</v>
+      </c>
+      <c r="C117" t="s">
+        <v>621</v>
+      </c>
+      <c r="D117" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" t="s">
+        <v>123</v>
+      </c>
+      <c r="F117" t="s">
+        <v>622</v>
+      </c>
+      <c r="G117" t="s">
+        <v>623</v>
+      </c>
+      <c r="H117" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>625</v>
+      </c>
+      <c r="B118" t="s">
+        <v>183</v>
+      </c>
+      <c r="C118" t="s">
+        <v>626</v>
+      </c>
+      <c r="D118" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" t="s">
+        <v>123</v>
+      </c>
+      <c r="F118" t="s">
+        <v>627</v>
+      </c>
+      <c r="G118" t="s">
+        <v>628</v>
+      </c>
+      <c r="H118" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>630</v>
+      </c>
+      <c r="B119" t="s">
+        <v>183</v>
+      </c>
+      <c r="C119" t="s">
+        <v>631</v>
+      </c>
+      <c r="D119" t="s">
+        <v>11</v>
+      </c>
+      <c r="E119" t="s">
+        <v>123</v>
+      </c>
+      <c r="F119" t="s">
+        <v>632</v>
+      </c>
+      <c r="G119" t="s">
+        <v>633</v>
+      </c>
+      <c r="H119" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>635</v>
+      </c>
+      <c r="B120" t="s">
+        <v>183</v>
+      </c>
+      <c r="C120" t="s">
+        <v>636</v>
+      </c>
+      <c r="D120" t="s">
+        <v>11</v>
+      </c>
+      <c r="E120" t="s">
+        <v>123</v>
+      </c>
+      <c r="F120" t="s">
+        <v>637</v>
+      </c>
+      <c r="G120" t="s">
+        <v>262</v>
+      </c>
+      <c r="H120" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>639</v>
+      </c>
+      <c r="B121" t="s">
+        <v>183</v>
+      </c>
+      <c r="C121" t="s">
+        <v>640</v>
+      </c>
+      <c r="D121" t="s">
+        <v>11</v>
+      </c>
+      <c r="E121" t="s">
+        <v>123</v>
+      </c>
+      <c r="F121" t="s">
+        <v>641</v>
+      </c>
+      <c r="G121" t="s">
+        <v>642</v>
+      </c>
+      <c r="H121" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>644</v>
+      </c>
+      <c r="B122" t="s">
+        <v>183</v>
+      </c>
+      <c r="C122" t="s">
+        <v>645</v>
+      </c>
+      <c r="D122" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" t="s">
+        <v>123</v>
+      </c>
+      <c r="F122" t="s">
+        <v>646</v>
+      </c>
+      <c r="G122" t="s">
+        <v>647</v>
+      </c>
+      <c r="H122" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>649</v>
+      </c>
+      <c r="B123" t="s">
+        <v>183</v>
+      </c>
+      <c r="C123" t="s">
+        <v>650</v>
+      </c>
+      <c r="D123" t="s">
+        <v>11</v>
+      </c>
+      <c r="E123" t="s">
+        <v>123</v>
+      </c>
+      <c r="F123" t="s">
+        <v>651</v>
+      </c>
+      <c r="G123" t="s">
+        <v>652</v>
+      </c>
+      <c r="H123" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>654</v>
+      </c>
+      <c r="B124" t="s">
+        <v>183</v>
+      </c>
+      <c r="C124" t="s">
+        <v>655</v>
+      </c>
+      <c r="D124" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" t="s">
+        <v>123</v>
+      </c>
+      <c r="F124" t="s">
+        <v>656</v>
+      </c>
+      <c r="G124" t="s">
+        <v>657</v>
+      </c>
+      <c r="H124" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>659</v>
+      </c>
+      <c r="B125" t="s">
+        <v>183</v>
+      </c>
+      <c r="C125" t="s">
+        <v>660</v>
+      </c>
+      <c r="D125" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" t="s">
+        <v>123</v>
+      </c>
+      <c r="F125" t="s">
+        <v>661</v>
+      </c>
+      <c r="G125" t="s">
+        <v>662</v>
+      </c>
+      <c r="H125" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>664</v>
+      </c>
+      <c r="B126" t="s">
+        <v>183</v>
+      </c>
+      <c r="C126" t="s">
+        <v>665</v>
+      </c>
+      <c r="D126" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126" t="s">
+        <v>123</v>
+      </c>
+      <c r="F126" t="s">
+        <v>666</v>
+      </c>
+      <c r="G126" t="s">
+        <v>667</v>
+      </c>
+      <c r="H126" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>669</v>
+      </c>
+      <c r="B127" t="s">
+        <v>183</v>
+      </c>
+      <c r="C127" t="s">
+        <v>670</v>
+      </c>
+      <c r="D127" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" t="s">
+        <v>123</v>
+      </c>
+      <c r="F127" t="s">
+        <v>671</v>
+      </c>
+      <c r="G127" t="s">
+        <v>672</v>
+      </c>
+      <c r="H127" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>674</v>
+      </c>
+      <c r="B128" t="s">
+        <v>183</v>
+      </c>
+      <c r="C128" t="s">
+        <v>675</v>
+      </c>
+      <c r="D128" t="s">
+        <v>11</v>
+      </c>
+      <c r="E128" t="s">
+        <v>123</v>
+      </c>
+      <c r="F128" t="s">
+        <v>676</v>
+      </c>
+      <c r="G128" t="s">
+        <v>677</v>
+      </c>
+      <c r="H128" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>679</v>
+      </c>
+      <c r="B129" t="s">
+        <v>183</v>
+      </c>
+      <c r="C129" t="s">
+        <v>680</v>
+      </c>
+      <c r="D129" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" t="s">
+        <v>123</v>
+      </c>
+      <c r="F129" t="s">
+        <v>681</v>
+      </c>
+      <c r="G129" t="s">
+        <v>682</v>
+      </c>
+      <c r="H129" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>684</v>
+      </c>
+      <c r="B130" t="s">
+        <v>183</v>
+      </c>
+      <c r="C130" t="s">
+        <v>685</v>
+      </c>
+      <c r="D130" t="s">
+        <v>11</v>
+      </c>
+      <c r="E130" t="s">
+        <v>123</v>
+      </c>
+      <c r="F130" t="s">
+        <v>686</v>
+      </c>
+      <c r="G130" t="s">
+        <v>687</v>
+      </c>
+      <c r="H130" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>689</v>
+      </c>
+      <c r="B131" t="s">
+        <v>183</v>
+      </c>
+      <c r="C131" t="s">
+        <v>690</v>
+      </c>
+      <c r="D131" t="s">
+        <v>11</v>
+      </c>
+      <c r="E131" t="s">
+        <v>123</v>
+      </c>
+      <c r="F131" t="s">
+        <v>691</v>
+      </c>
+      <c r="G131" t="s">
+        <v>692</v>
+      </c>
+      <c r="H131" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>694</v>
+      </c>
+      <c r="B132" t="s">
+        <v>183</v>
+      </c>
+      <c r="C132" t="s">
+        <v>695</v>
+      </c>
+      <c r="D132" t="s">
+        <v>11</v>
+      </c>
+      <c r="E132" t="s">
+        <v>123</v>
+      </c>
+      <c r="F132" t="s">
+        <v>696</v>
+      </c>
+      <c r="G132" t="s">
+        <v>697</v>
+      </c>
+      <c r="H132" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>699</v>
+      </c>
+      <c r="B133" t="s">
+        <v>183</v>
+      </c>
+      <c r="C133" t="s">
+        <v>700</v>
+      </c>
+      <c r="D133" t="s">
+        <v>11</v>
+      </c>
+      <c r="E133" t="s">
+        <v>123</v>
+      </c>
+      <c r="F133" t="s">
+        <v>701</v>
+      </c>
+      <c r="G133" t="s">
+        <v>702</v>
+      </c>
+      <c r="H133" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>704</v>
+      </c>
+      <c r="B134" t="s">
+        <v>183</v>
+      </c>
+      <c r="C134" t="s">
+        <v>705</v>
+      </c>
+      <c r="D134" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" t="s">
+        <v>123</v>
+      </c>
+      <c r="F134" t="s">
+        <v>706</v>
+      </c>
+      <c r="G134" t="s">
+        <v>707</v>
+      </c>
+      <c r="H134" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>709</v>
+      </c>
+      <c r="B135" t="s">
+        <v>183</v>
+      </c>
+      <c r="C135" t="s">
+        <v>710</v>
+      </c>
+      <c r="D135" t="s">
+        <v>11</v>
+      </c>
+      <c r="E135" t="s">
+        <v>123</v>
+      </c>
+      <c r="F135" t="s">
+        <v>711</v>
+      </c>
+      <c r="G135" t="s">
+        <v>712</v>
+      </c>
+      <c r="H135" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>714</v>
+      </c>
+      <c r="B136" t="s">
+        <v>183</v>
+      </c>
+      <c r="C136" t="s">
+        <v>715</v>
+      </c>
+      <c r="D136" t="s">
+        <v>11</v>
+      </c>
+      <c r="E136" t="s">
+        <v>123</v>
+      </c>
+      <c r="F136" t="s">
+        <v>716</v>
+      </c>
+      <c r="G136" t="s">
+        <v>717</v>
+      </c>
+      <c r="H136" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>719</v>
+      </c>
+      <c r="B137" t="s">
+        <v>183</v>
+      </c>
+      <c r="C137" t="s">
+        <v>720</v>
+      </c>
+      <c r="D137" t="s">
+        <v>11</v>
+      </c>
+      <c r="E137" t="s">
+        <v>123</v>
+      </c>
+      <c r="F137" t="s">
+        <v>721</v>
+      </c>
+      <c r="G137" t="s">
+        <v>722</v>
+      </c>
+      <c r="H137" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>724</v>
+      </c>
+      <c r="B138" t="s">
+        <v>183</v>
+      </c>
+      <c r="C138" t="s">
+        <v>725</v>
+      </c>
+      <c r="D138" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" t="s">
+        <v>123</v>
+      </c>
+      <c r="F138" t="s">
+        <v>726</v>
+      </c>
+      <c r="G138" t="s">
+        <v>727</v>
+      </c>
+      <c r="H138" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>729</v>
+      </c>
+      <c r="B139" t="s">
+        <v>183</v>
+      </c>
+      <c r="C139" t="s">
+        <v>730</v>
+      </c>
+      <c r="D139" t="s">
+        <v>11</v>
+      </c>
+      <c r="E139" t="s">
+        <v>123</v>
+      </c>
+      <c r="F139" t="s">
+        <v>731</v>
+      </c>
+      <c r="G139" t="s">
+        <v>732</v>
+      </c>
+      <c r="H139" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>734</v>
+      </c>
+      <c r="B140" t="s">
+        <v>183</v>
+      </c>
+      <c r="C140" t="s">
+        <v>735</v>
+      </c>
+      <c r="D140" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" t="s">
+        <v>123</v>
+      </c>
+      <c r="F140" t="s">
+        <v>736</v>
+      </c>
+      <c r="G140" t="s">
+        <v>737</v>
+      </c>
+      <c r="H140" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>739</v>
+      </c>
+      <c r="B141" t="s">
+        <v>183</v>
+      </c>
+      <c r="C141" t="s">
+        <v>740</v>
+      </c>
+      <c r="D141" t="s">
+        <v>11</v>
+      </c>
+      <c r="E141" t="s">
+        <v>123</v>
+      </c>
+      <c r="F141" t="s">
+        <v>741</v>
+      </c>
+      <c r="G141" t="s">
+        <v>742</v>
+      </c>
+      <c r="H141" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>744</v>
+      </c>
+      <c r="B142" t="s">
+        <v>183</v>
+      </c>
+      <c r="C142" t="s">
+        <v>745</v>
+      </c>
+      <c r="D142" t="s">
+        <v>11</v>
+      </c>
+      <c r="E142" t="s">
+        <v>123</v>
+      </c>
+      <c r="F142" t="s">
+        <v>746</v>
+      </c>
+      <c r="G142" t="s">
+        <v>747</v>
+      </c>
+      <c r="H142" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>749</v>
+      </c>
+      <c r="B143" t="s">
+        <v>183</v>
+      </c>
+      <c r="C143" t="s">
+        <v>750</v>
+      </c>
+      <c r="D143" t="s">
+        <v>11</v>
+      </c>
+      <c r="E143" t="s">
+        <v>123</v>
+      </c>
+      <c r="F143" t="s">
+        <v>751</v>
+      </c>
+      <c r="G143" t="s">
+        <v>752</v>
+      </c>
+      <c r="H143" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>754</v>
+      </c>
+      <c r="B144" t="s">
+        <v>183</v>
+      </c>
+      <c r="C144" t="s">
+        <v>755</v>
+      </c>
+      <c r="D144" t="s">
+        <v>11</v>
+      </c>
+      <c r="E144" t="s">
+        <v>123</v>
+      </c>
+      <c r="F144" t="s">
+        <v>756</v>
+      </c>
+      <c r="G144" t="s">
+        <v>757</v>
+      </c>
+      <c r="H144" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>759</v>
+      </c>
+      <c r="B145" t="s">
+        <v>183</v>
+      </c>
+      <c r="C145" t="s">
+        <v>760</v>
+      </c>
+      <c r="D145" t="s">
+        <v>11</v>
+      </c>
+      <c r="E145" t="s">
+        <v>123</v>
+      </c>
+      <c r="F145" t="s">
+        <v>761</v>
+      </c>
+      <c r="G145" t="s">
+        <v>762</v>
+      </c>
+      <c r="H145" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>764</v>
+      </c>
+      <c r="B146" t="s">
+        <v>183</v>
+      </c>
+      <c r="C146" t="s">
+        <v>765</v>
+      </c>
+      <c r="D146" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" t="s">
+        <v>123</v>
+      </c>
+      <c r="F146" t="s">
+        <v>766</v>
+      </c>
+      <c r="G146" t="s">
+        <v>767</v>
+      </c>
+      <c r="H146" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>769</v>
+      </c>
+      <c r="B147" t="s">
+        <v>183</v>
+      </c>
+      <c r="C147" t="s">
+        <v>770</v>
+      </c>
+      <c r="D147" t="s">
+        <v>11</v>
+      </c>
+      <c r="E147" t="s">
+        <v>123</v>
+      </c>
+      <c r="F147" t="s">
+        <v>771</v>
+      </c>
+      <c r="G147" t="s">
+        <v>772</v>
+      </c>
+      <c r="H147" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>774</v>
+      </c>
+      <c r="B148" t="s">
+        <v>183</v>
+      </c>
+      <c r="C148" t="s">
+        <v>775</v>
+      </c>
+      <c r="D148" t="s">
+        <v>11</v>
+      </c>
+      <c r="E148" t="s">
+        <v>123</v>
+      </c>
+      <c r="F148" t="s">
+        <v>776</v>
+      </c>
+      <c r="G148" t="s">
+        <v>777</v>
+      </c>
+      <c r="H148" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>779</v>
+      </c>
+      <c r="B149" t="s">
+        <v>183</v>
+      </c>
+      <c r="C149" t="s">
+        <v>780</v>
+      </c>
+      <c r="D149" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" t="s">
+        <v>123</v>
+      </c>
+      <c r="F149" t="s">
+        <v>781</v>
+      </c>
+      <c r="G149" t="s">
+        <v>782</v>
+      </c>
+      <c r="H149" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>784</v>
+      </c>
+      <c r="B150" t="s">
+        <v>183</v>
+      </c>
+      <c r="C150" t="s">
+        <v>785</v>
+      </c>
+      <c r="D150" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" t="s">
+        <v>123</v>
+      </c>
+      <c r="F150" t="s">
+        <v>786</v>
+      </c>
+      <c r="G150" t="s">
+        <v>787</v>
+      </c>
+      <c r="H150" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>789</v>
+      </c>
+      <c r="B151" t="s">
+        <v>183</v>
+      </c>
+      <c r="C151" t="s">
+        <v>790</v>
+      </c>
+      <c r="D151" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" t="s">
+        <v>123</v>
+      </c>
+      <c r="F151" t="s">
+        <v>791</v>
+      </c>
+      <c r="G151" t="s">
+        <v>792</v>
+      </c>
+      <c r="H151" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>794</v>
+      </c>
+      <c r="B152" t="s">
+        <v>183</v>
+      </c>
+      <c r="C152" t="s">
+        <v>795</v>
+      </c>
+      <c r="D152" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" t="s">
+        <v>123</v>
+      </c>
+      <c r="F152" t="s">
+        <v>796</v>
+      </c>
+      <c r="G152" t="s">
+        <v>797</v>
+      </c>
+      <c r="H152" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>799</v>
+      </c>
+      <c r="B153" t="s">
+        <v>183</v>
+      </c>
+      <c r="C153" t="s">
+        <v>800</v>
+      </c>
+      <c r="D153" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" t="s">
+        <v>123</v>
+      </c>
+      <c r="F153" t="s">
+        <v>801</v>
+      </c>
+      <c r="G153" t="s">
+        <v>802</v>
+      </c>
+      <c r="H153" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>804</v>
+      </c>
+      <c r="B154" t="s">
+        <v>183</v>
+      </c>
+      <c r="C154" t="s">
+        <v>805</v>
+      </c>
+      <c r="D154" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" t="s">
+        <v>123</v>
+      </c>
+      <c r="F154" t="s">
+        <v>806</v>
+      </c>
+      <c r="G154" t="s">
+        <v>807</v>
+      </c>
+      <c r="H154" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>809</v>
+      </c>
+      <c r="B155" t="s">
+        <v>183</v>
+      </c>
+      <c r="C155" t="s">
+        <v>810</v>
+      </c>
+      <c r="D155" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" t="s">
+        <v>123</v>
+      </c>
+      <c r="F155" t="s">
+        <v>811</v>
+      </c>
+      <c r="G155" t="s">
+        <v>812</v>
+      </c>
+      <c r="H155" t="s">
+        <v>813</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-standalone.report.xlsx
+++ b/tools/importer/reports/import-standalone.report.xlsx
@@ -40,7 +40,7 @@
     <t>about.report.json</t>
   </si>
   <si>
-    <t>["cards-article"]</t>
+    <t>["cards-timeline"]</t>
   </si>
   <si>
     <t>about</t>
@@ -52,7 +52,7 @@
     <t>standalone</t>
   </si>
   <si>
-    <t>2026-06-28T17:49:20.218Z</t>
+    <t>2026-06-29T05:06:54.954Z</t>
   </si>
   <si>
     <t>About Us | MOOG Parts</t>

--- a/tools/importer/reports/import-standalone.report.xlsx
+++ b/tools/importer/reports/import-standalone.report.xlsx
@@ -52,7 +52,7 @@
     <t>standalone</t>
   </si>
   <si>
-    <t>2026-06-29T05:06:54.954Z</t>
+    <t>2026-06-29T05:13:34.702Z</t>
   </si>
   <si>
     <t>About Us | MOOG Parts</t>

--- a/tools/importer/reports/import-standalone.report.xlsx
+++ b/tools/importer/reports/import-standalone.report.xlsx
@@ -175,7 +175,7 @@
     <t>light-commercial-vehicle</t>
   </si>
   <si>
-    <t>2026-06-28T17:50:01.100Z</t>
+    <t>2026-06-29T06:05:23.898Z</t>
   </si>
   <si>
     <t>Light Commercial Vehicle | MOOG Parts</t>
@@ -217,7 +217,7 @@
     <t>parts-matter-index</t>
   </si>
   <si>
-    <t>2026-06-28T17:29:56.231Z</t>
+    <t>2026-06-29T05:48:29.638Z</t>
   </si>
   <si>
     <t>Aftermarket Auto Parts Tips &amp; Articles | MOOG Parts</t>
@@ -238,7 +238,7 @@
     <t>parts-landing</t>
   </si>
   <si>
-    <t>2026-06-28T14:23:40.691Z</t>
+    <t>2026-06-29T05:57:40.168Z</t>
   </si>
   <si>
     <t>Performance Aftermarket Chassis &amp; Auto Parts | MOOG Parts</t>
